--- a/WorkBot/refactor-experimental/data/orders/Peters Supply/Peters Supply_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Peters Supply/Peters Supply_Downtown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Bag - Paper (20# Squat)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>24.71</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.71</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Bag - Paper (6#)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>12.57</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12.57</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Glove Nitrile - Large</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26.25</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Glove Nitrile - Med</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26.25</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Glove Nitrile - XLarge</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.25</v>
       </c>
     </row>
   </sheetData>
